--- a/Compititor's_Price/Cladco_Prices/Cladco_Prices_28-11-2025.xlsx
+++ b/Compititor's_Price/Cladco_Prices/Cladco_Prices_28-11-2025.xlsx
@@ -483,7 +483,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-hollow-grooved-composite-decking-board-in-charcoal</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -535,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -572,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -594,7 +602,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/22-hollow-domestic-grade</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,7 +625,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -646,7 +662,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -683,7 +699,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -720,7 +736,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -757,7 +773,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -779,7 +795,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -794,7 +818,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -816,7 +840,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -831,7 +863,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -853,7 +885,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -868,7 +908,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -890,7 +930,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -905,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -927,7 +975,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -942,7 +998,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -964,7 +1020,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -979,7 +1043,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1065,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1016,7 +1088,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1110,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1053,7 +1133,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1155,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1090,7 +1178,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1200,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1127,7 +1223,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1245,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1164,7 +1268,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1290,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1201,7 +1313,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1335,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1238,7 +1358,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1380,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1275,7 +1403,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1425,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1312,7 +1448,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1470,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1349,7 +1493,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1515,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1386,7 +1538,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1560,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1423,7 +1583,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1605,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1460,7 +1628,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1650,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1497,7 +1673,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1695,15 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1534,7 +1718,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1740,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1571,7 +1763,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1785,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1608,7 +1808,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1830,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1645,7 +1853,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1890,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1912,15 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1719,7 +1935,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1972,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1793,7 +2009,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1815,7 +2031,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1830,7 +2054,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1852,7 +2076,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1867,7 +2099,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2136,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2173,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2190,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1978,7 +2210,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2232,15 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2015,7 +2255,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2277,15 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2052,7 +2300,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2322,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2089,7 +2345,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2367,15 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2126,7 +2390,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2412,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2163,7 +2435,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2457,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2200,7 +2480,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2502,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2237,7 +2525,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2547,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2274,7 +2570,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2592,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2311,7 +2615,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2637,15 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2348,7 +2660,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2682,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2385,7 +2705,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2727,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2422,7 +2750,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2772,15 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2459,7 +2795,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2817,15 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2496,7 +2840,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2862,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2533,7 +2885,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2907,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2570,7 +2930,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2952,15 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2607,7 +2975,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2997,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2644,7 +3020,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2666,7 +3042,15 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2681,7 +3065,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2703,7 +3087,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2718,7 +3110,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2740,7 +3132,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2755,7 +3155,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2777,7 +3177,15 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2792,7 +3200,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3222,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2829,7 +3245,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2851,7 +3267,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2866,7 +3290,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2888,7 +3312,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2903,7 +3335,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2925,7 +3357,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2940,7 +3380,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3402,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2977,7 +3425,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3447,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3014,7 +3470,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3492,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3051,7 +3515,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3537,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3088,7 +3560,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3582,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3125,7 +3605,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3627,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3162,7 +3650,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3672,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3199,7 +3695,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3717,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3236,7 +3740,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3762,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-joists-batten</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3273,7 +3785,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3807,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/structural-composite-joist</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3310,7 +3830,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3852,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-starter-clips-pack-of-50</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3347,7 +3875,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3897,15 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-t-clip-fixings-and-screws</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3406,7 +3942,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-stainless-clips</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3421,7 +3965,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3987,15 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/m4-40mm-stainless-steel-fibre-cement</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3458,7 +4010,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3480,7 +4032,15 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-heavy-duty-weed-control-mat</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3495,7 +4055,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3517,7 +4077,15 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-weed-mat-pins</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3532,7 +4100,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3554,7 +4122,15 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-composite-decking-cleaner</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3569,7 +4145,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3586,12 +4162,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3606,7 +4190,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3623,12 +4207,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3643,7 +4235,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3660,7 +4252,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3680,7 +4272,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3702,7 +4294,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/universal-sealant-gun-310ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3717,7 +4317,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3739,7 +4339,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3776,7 +4384,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3813,7 +4429,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3850,7 +4474,15 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3887,7 +4519,15 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3924,7 +4564,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3961,7 +4609,15 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3998,7 +4654,15 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4035,7 +4699,15 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4072,7 +4744,15 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4109,7 +4789,15 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4146,7 +4834,15 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4161,7 +4857,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>£17.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.kellaway.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4879,15 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4198,7 +4902,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>£17.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.kellaway.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4924,15 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4235,7 +4947,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>£17.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.kellaway.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4969,15 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4272,7 +4992,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>£17.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.kellaway.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
     </row>
@@ -4294,7 +5014,15 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4309,7 +5037,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>£17.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.kellaway.co.uk', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
     </row>
@@ -4331,7 +5059,15 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding-starter-strip</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4346,7 +5082,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4368,7 +5104,15 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4383,7 +5127,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4405,7 +5149,15 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4420,7 +5172,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4442,7 +5194,15 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4457,7 +5217,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4479,7 +5239,15 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4494,7 +5262,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4516,7 +5284,15 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4531,7 +5307,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4553,7 +5329,15 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4568,7 +5352,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4590,7 +5374,15 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4605,7 +5397,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4627,7 +5419,15 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4642,7 +5442,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4664,7 +5464,15 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4679,7 +5487,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4701,7 +5509,15 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4716,7 +5532,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4733,12 +5549,20 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>£6.27</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4753,7 +5577,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4775,7 +5599,15 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4790,7 +5622,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4812,7 +5644,15 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4827,7 +5667,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4849,7 +5689,15 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4864,7 +5712,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4886,7 +5734,15 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4901,7 +5757,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4923,7 +5779,15 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4938,7 +5802,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5824,15 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4975,7 +5847,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5869,15 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5012,7 +5892,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5909,20 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5049,7 +5937,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5959,15 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5086,7 +5982,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5108,7 +6004,15 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5123,7 +6027,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5145,7 +6049,15 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5160,7 +6072,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5182,7 +6094,15 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5197,7 +6117,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5219,7 +6139,15 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5234,7 +6162,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5256,7 +6184,15 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5271,7 +6207,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5293,7 +6229,15 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5308,7 +6252,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5330,7 +6274,15 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5345,7 +6297,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5367,7 +6319,15 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5382,7 +6342,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5404,7 +6364,15 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5419,7 +6387,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5441,7 +6409,15 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5456,7 +6432,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5478,7 +6454,15 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5493,7 +6477,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5515,7 +6499,15 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5530,7 +6522,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5552,7 +6544,15 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5567,7 +6567,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5589,7 +6589,15 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5604,7 +6612,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5626,7 +6634,15 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5641,7 +6657,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5663,7 +6679,15 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5678,7 +6702,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5700,7 +6724,15 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5715,7 +6747,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5737,7 +6769,15 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5752,7 +6792,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5774,7 +6814,15 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5789,7 +6837,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5806,12 +6854,20 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5826,7 +6882,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5848,7 +6904,15 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3m-aluminium-perforated-closure</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5863,7 +6927,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5885,7 +6949,15 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5900,7 +6972,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5922,7 +6994,15 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5937,7 +7017,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5959,7 +7039,15 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5974,7 +7062,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5996,7 +7084,15 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6011,7 +7107,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6033,7 +7129,15 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6048,7 +7152,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6070,7 +7174,15 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6085,7 +7197,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6107,7 +7219,15 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6122,7 +7242,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6144,7 +7264,15 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6159,7 +7287,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6181,7 +7309,15 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6196,7 +7332,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6218,7 +7354,15 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6233,7 +7377,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6255,7 +7399,15 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6270,7 +7422,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6292,7 +7444,15 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6307,7 +7467,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6329,7 +7489,15 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6344,7 +7512,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6366,7 +7534,15 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6381,7 +7557,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6403,7 +7579,15 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6418,7 +7602,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6440,7 +7624,15 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6455,7 +7647,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6477,7 +7669,15 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6492,7 +7692,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6514,7 +7714,15 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6529,7 +7737,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6551,7 +7759,15 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6566,7 +7782,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6588,7 +7804,15 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6603,7 +7827,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6625,7 +7849,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6640,7 +7872,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6662,7 +7894,15 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6677,7 +7917,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6699,7 +7939,15 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6714,7 +7962,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6736,7 +7984,15 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6751,7 +8007,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6773,7 +8029,15 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6788,7 +8052,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6810,7 +8074,15 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6825,7 +8097,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6847,7 +8119,15 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6862,7 +8142,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6884,7 +8164,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6899,7 +8187,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6921,7 +8209,15 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6936,7 +8232,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6958,7 +8254,15 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6973,7 +8277,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6995,7 +8299,15 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7010,7 +8322,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7032,7 +8344,15 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7047,7 +8367,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7069,7 +8389,15 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7084,7 +8412,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7106,7 +8434,15 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7121,7 +8457,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7143,7 +8479,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7158,7 +8502,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7180,7 +8524,15 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7195,7 +8547,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7217,7 +8569,15 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7232,7 +8592,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7254,7 +8614,15 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7269,7 +8637,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7291,7 +8659,15 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7306,7 +8682,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7328,7 +8704,15 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7343,7 +8727,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7365,7 +8749,15 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7380,7 +8772,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7402,7 +8794,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7417,7 +8817,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7439,7 +8839,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7454,7 +8862,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7476,7 +8884,15 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7491,7 +8907,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7513,7 +8929,15 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7528,7 +8952,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7550,7 +8974,15 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7565,7 +8997,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7587,7 +9019,15 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7602,7 +9042,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7624,7 +9064,15 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7639,7 +9087,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7661,7 +9109,15 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7676,7 +9132,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7698,7 +9154,15 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7713,7 +9177,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7735,7 +9199,15 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7750,7 +9222,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7772,7 +9244,15 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7787,7 +9267,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7809,7 +9289,15 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7824,7 +9312,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7846,7 +9334,15 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7861,7 +9357,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7883,7 +9379,15 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7898,7 +9402,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7920,7 +9424,15 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7935,7 +9447,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7957,7 +9469,15 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7972,7 +9492,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7994,7 +9514,15 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8009,7 +9537,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8031,7 +9559,15 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8046,7 +9582,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8068,7 +9604,15 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8083,7 +9627,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8105,7 +9649,15 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -8120,7 +9672,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8142,7 +9694,15 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -8157,7 +9717,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8179,7 +9739,15 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8194,7 +9762,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8216,7 +9784,15 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8231,7 +9807,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8253,7 +9829,15 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -8268,7 +9852,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8290,7 +9874,15 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -8305,7 +9897,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8327,7 +9919,15 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -8342,7 +9942,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8364,7 +9964,15 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -8379,7 +9987,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8401,7 +10009,15 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-black-balustrade-handrail-post</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -8416,7 +10032,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8438,7 +10054,15 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/balustrade-handrail-gate-aluminium-powder-coated-material</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8453,7 +10077,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8490,7 +10114,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8527,7 +10151,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8564,7 +10188,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8586,7 +10210,15 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-cladding-batten-50mm-x-50mm-x-3m-length-black</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8601,7 +10233,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8623,7 +10255,15 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-post-100x100</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8638,7 +10278,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8660,7 +10300,15 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-joist-50mm-x-100mm-x-3-6m-length-black</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8675,7 +10323,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8697,7 +10345,15 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-joist-50x150-3m-black</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8712,7 +10368,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8734,7 +10390,15 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/frame-protection-deck-tape-65mm-x-20m-roll-black</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8749,7 +10413,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8771,7 +10435,15 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8786,7 +10458,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8808,7 +10480,15 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8823,7 +10503,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8845,7 +10525,15 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8860,7 +10548,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8882,7 +10570,15 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8897,7 +10593,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8919,7 +10615,15 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8934,7 +10638,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8956,7 +10660,15 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8971,7 +10683,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8993,7 +10705,15 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9008,7 +10728,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9030,7 +10750,15 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9045,7 +10773,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9067,7 +10795,15 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9082,7 +10818,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9104,7 +10840,15 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9119,7 +10863,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9141,7 +10885,15 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9156,7 +10908,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9178,7 +10930,15 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t>Error: BrowserType.launch: Executable doesn't exist at C:\Users\Priyanka\AppData\Local\ms-playwright\chromium_headless_shell-1194\chrome-win\headless_shell.exe
+╔════════════════════════════════════════════════════════════╗
+║ Looks like Playwright was just installed or updated.       ║
+║ Please run the following command to download new browsers: ║
+║                                                            ║
+║     playwright install                                     ║
+║                                                            ║
+║ &lt;3 Playwright Team                                         ║
+╚════════════════════════════════════════════════════════════╝</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -9193,7 +10953,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
